--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.97</v>
+        <v>92.41</v>
       </c>
       <c r="C2" t="n">
-        <v>57.11</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>8.17</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>210.52</v>
+        <v>205.38</v>
       </c>
       <c r="C3" t="n">
-        <v>197.96</v>
+        <v>182.57</v>
       </c>
       <c r="D3" t="n">
-        <v>11.57</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>926.4</v>
+        <v>859.64</v>
       </c>
       <c r="C4" t="n">
-        <v>705.28</v>
+        <v>635.4400000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>24.06</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.03</v>
+        <v>133.22</v>
       </c>
       <c r="C5" t="n">
-        <v>54.95</v>
+        <v>102.92</v>
       </c>
       <c r="D5" t="n">
-        <v>4.96</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>433.32</v>
+        <v>359.24</v>
       </c>
       <c r="C6" t="n">
-        <v>379.98</v>
+        <v>328.34</v>
       </c>
       <c r="D6" t="n">
-        <v>31.59</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.42</v>
+        <v>1.17</v>
       </c>
       <c r="C7" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="C8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>20.43</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.71</v>
+        <v>22.5</v>
       </c>
       <c r="C9" t="n">
-        <v>27.82</v>
+        <v>16.04</v>
       </c>
       <c r="D9" t="n">
-        <v>23.32</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="10">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280.72</v>
+        <v>270.56</v>
       </c>
       <c r="C10" t="n">
-        <v>243.72</v>
+        <v>235.79</v>
       </c>
       <c r="D10" t="n">
-        <v>8.109999999999999</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="11">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>125.4</v>
+        <v>114.52</v>
       </c>
       <c r="C11" t="n">
-        <v>101.16</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>6.58</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="12">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>308.64</v>
+        <v>216.41</v>
       </c>
       <c r="C12" t="n">
-        <v>259.47</v>
+        <v>174.38</v>
       </c>
       <c r="D12" t="n">
-        <v>22.82</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="13">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.56</v>
+        <v>66.22</v>
       </c>
       <c r="C13" t="n">
-        <v>47.3</v>
+        <v>52.76</v>
       </c>
       <c r="D13" t="n">
-        <v>17.37</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="14">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85.16</v>
+        <v>80.94</v>
       </c>
       <c r="C14" t="n">
-        <v>70.65000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="15">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.32</v>
+        <v>28.5</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69</v>
+        <v>24.32</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="16">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>921.63</v>
+        <v>683.26</v>
       </c>
       <c r="C16" t="n">
-        <v>733.26</v>
+        <v>508.75</v>
       </c>
       <c r="D16" t="n">
-        <v>38.76</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1252.52</v>
+        <v>840.11</v>
       </c>
       <c r="C17" t="n">
-        <v>1071.33</v>
+        <v>607.89</v>
       </c>
       <c r="D17" t="n">
-        <v>69.48</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>426.75</v>
+        <v>703.4</v>
       </c>
       <c r="C18" t="n">
-        <v>351.16</v>
+        <v>492.07</v>
       </c>
       <c r="D18" t="n">
-        <v>64.90000000000001</v>
+        <v>106.59</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107.04</v>
+        <v>105.56</v>
       </c>
       <c r="C19" t="n">
-        <v>86.29000000000001</v>
+        <v>81.94</v>
       </c>
       <c r="D19" t="n">
-        <v>10.05</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49.52</v>
+        <v>50.74</v>
       </c>
       <c r="C20" t="n">
-        <v>46.4</v>
+        <v>46.1</v>
       </c>
       <c r="D20" t="n">
-        <v>12.14</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>864.2</v>
+        <v>862.34</v>
       </c>
       <c r="C21" t="n">
-        <v>724.77</v>
+        <v>669.5700000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>11.24</v>
       </c>
     </row>
   </sheetData>
